--- a/samples/ss_pedan34_ingest.xlsx
+++ b/samples/ss_pedan34_ingest.xlsx
@@ -984,7 +984,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SUTT Kanetug - Godean (belum energize)</t>
+          <t>SUTT Kanetug - Godean</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2278,20 +2278,24 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SUTT Kanetug - Gajahan (arah SS Tanjung Jati)</t>
+          <t>SUTT Godean - Bantul</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KNTUG</t>
+          <t>GDEAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GJYAN</t>
+          <t>BANTL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2310,7 +2314,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -2321,10 +2325,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -2337,24 +2341,20 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUTT Pedan - Bantul</t>
+          <t>SUTT Kanetug - Gajahan (arah SS Tanjung Jati)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PEDAN</t>
+          <t>KNTUG</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BANTL</t>
+          <t>GJYAN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>

--- a/samples/ss_pedan34_ingest.xlsx
+++ b/samples/ss_pedan34_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_pedan34_ingest.xlsx
+++ b/samples/ss_pedan34_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 3,4 Pedan 500/150 kV</t>
+          <t>IBT 3 Pedan 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 3,4)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pedan (bus 150 kV)</t>
+          <t>IBT 4 Pedan 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 4 PEDAN7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PEDAN7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>PEDAN</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -774,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1;2</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -791,12 +805,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pacitan</t>
+          <t>Pedan (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PCTAN</t>
+          <t>PEDAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -844,17 +858,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLTU Pacitan</t>
+          <t>Pacitan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KIT_PCTAN</t>
+          <t>PCTAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -897,21 +911,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kanetug</t>
+          <t>PLTU Pacitan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KNTUG</t>
+          <t>KIT_PCTAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -933,14 +947,10 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -954,12 +964,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Godean</t>
+          <t>Kanetug</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GDEAN</t>
+          <t>KNTUG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -968,7 +978,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -995,7 +1005,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3;4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1011,12 +1021,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bantul</t>
+          <t>Godean</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BANTL</t>
+          <t>GDEAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1025,7 +1035,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1052,7 +1062,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3;4</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1068,12 +1078,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wonosari Bejan</t>
+          <t>Bantul</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WBJAN</t>
+          <t>BANTL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1082,7 +1092,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1098,16 +1108,20 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1121,12 +1135,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wonosari</t>
+          <t>Wonosari Bejan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WSARI</t>
+          <t>WBJAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1135,7 +1149,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1157,14 +1171,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1178,12 +1188,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Solo Baru</t>
+          <t>Wonosari</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SLBRU</t>
+          <t>WSARI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1192,7 +1202,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1219,7 +1229,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1235,12 +1245,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rayung</t>
+          <t>Solo Baru</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RAYUM</t>
+          <t>SLBRU</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1261,11 +1271,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>KTT RUM</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1280,7 +1286,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1296,12 +1302,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Palur</t>
+          <t>Rayung</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PALUR</t>
+          <t>RAYUM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1310,7 +1316,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1322,7 +1328,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>KTT RUM</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -1332,10 +1342,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1349,12 +1363,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Masaran</t>
+          <t>Palur</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MSRAN</t>
+          <t>PALUR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1363,7 +1377,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1385,14 +1399,10 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1406,12 +1416,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sragen</t>
+          <t>Masaran</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SRAGN</t>
+          <t>MSRAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1420,7 +1430,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1447,7 +1457,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1463,12 +1473,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ngunut/Ngadi</t>
+          <t>Sragen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NGTDI</t>
+          <t>SRAGN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1477,7 +1487,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,10 +1509,14 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -1516,12 +1530,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wonogiri</t>
+          <t>Ngunut/Ngadi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WNGRI</t>
+          <t>NGTDI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1530,7 +1544,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1569,12 +1583,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sugihrahayu/Mandari (SS Tanjung Jati)</t>
+          <t>Wonogiri</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SGRAH</t>
+          <t>WNGRI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1595,22 +1609,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Tanjung Jati 1,2 - Ungaran 3</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1630,12 +1636,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gajahan (SS Tanjung Jati)</t>
+          <t>Sugihrahayu/Mandari (SS Tanjung Jati)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GJYAN</t>
+          <t>SGRAH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1691,12 +1697,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wates (SS Kesugihan)</t>
+          <t>Gajahan (SS Tanjung Jati)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WATES</t>
+          <t>GJYAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1705,7 +1711,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1719,7 +1725,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Kesugihan 1,2</t>
+          <t>batas ke Subsistem Tanjung Jati 1,2 - Ungaran 3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1752,12 +1758,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Semanu (SS Pedan 1,2)</t>
+          <t>Wates (SS Kesugihan)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SMANU</t>
+          <t>WATES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1780,7 +1786,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Pedan 1,2</t>
+          <t>batas ke Subsistem Kesugihan 1,2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1813,12 +1819,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gondangrejo (SS Pedan 1,2)</t>
+          <t>Semanu (SS Pedan 1,2)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GDRJO</t>
+          <t>SMANU</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1874,12 +1880,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ngawi (SS Kediri)</t>
+          <t>Gondangrejo (SS Pedan 1,2)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NGAWI</t>
+          <t>GDRJO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1888,7 +1894,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1902,7 +1908,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>batas ke UP2B Jawa Timur (SS Kediri)</t>
+          <t>batas ke Subsistem Pedan 1,2</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1928,6 +1934,67 @@
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ngawi (SS Kediri)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NGAWI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>batas ke UP2B Jawa Timur (SS Kediri)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2525,7 +2592,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUTT Bantul - Wonosari Bejan (belum energize)</t>
+          <t>SKTT Bantul - Wonosari Bejan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2549,12 +2616,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -3343,12 +3410,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan IBT 1/2/3/4 GITET Pedan &gt;60% jika operasi looping IBT 1,2 dan 3,4 Pedan saat pemeliharaan pada salah satu IBT</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan IBT 1/2/3/4 GITET Pedan &gt;60% jika operasi looping IBT 1,2 dan 3,4 Pedan saat pemeliharaan pada salah satu IBT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3378,12 +3445,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Incomer di GI Godean dari Bay Kentungan dan Bantul terletak pada tower combined dan posisi line 1,2 masih atas-bawah sehingga menjadi tidak andal jika terjadi gangguan di ruas tersebut</t>
+          <t>[BELUM_DITETAPKAN] Incomer di GI Godean dari Bay Kentungan dan Bantul terletak pada tower combined dan posisi line 1,2 masih atas-bawah sehingga menjadi tidak andal jika terjadi gangguan di ruas tersebut</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3448,12 +3515,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Keandalan GI Rayum berkurang pada saat terjadi pekerjaan Pedan- Wonosari-Rayum</t>
+          <t>[BELUM_DITETAPKAN] Keandalan GI Rayum berkurang pada saat terjadi pekerjaan Pedan- Wonosari-Rayum</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3483,12 +3550,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Terdapat tegangan rendah (kurang dari 140 kV) di GI 150 kV Rayum yang berdampak pada kualitas tegangan</t>
+          <t>[BELUM_DITETAPKAN] Terdapat tegangan rendah (kurang dari 140 kV) di GI 150 kV Rayum yang berdampak pada kualitas tegangan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3553,12 +3620,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] GI 150 kV Bantul merupakan GI Simpul yang menghubungkan GI 150 kV Semanu dan GI 150 kV Wirobrajan secara radial dan penghubung antara Subsistem Pedan 1,2,3,4 dan Subsistem Kesugihan, sehingga pekerjaan yang membutuhkan padam Busbar tidak dapat dilakukan</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV Bantul merupakan GI Simpul yang menghubungkan GI 150 kV Semanu dan GI 150 kV Wirobrajan secara radial dan penghubung antara Subsistem Pedan 1,2,3,4 dan Subsistem Kesugihan, sehingga pekerjaan yang membutuhkan padam Busbar tidak dapat dilakukan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
